--- a/output/yearly_population_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_51_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5821</v>
+        <v>4724</v>
       </c>
       <c r="C2" t="n">
-        <v>10835</v>
+        <v>12475</v>
       </c>
       <c r="D2" t="n">
-        <v>23659</v>
+        <v>44048</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3856</v>
+        <v>3057</v>
       </c>
       <c r="C3" t="n">
-        <v>6223</v>
+        <v>10538</v>
       </c>
       <c r="D3" t="n">
-        <v>10952</v>
+        <v>15002</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3122</v>
+        <v>2579</v>
       </c>
       <c r="C4" t="n">
-        <v>7293</v>
+        <v>7874</v>
       </c>
       <c r="D4" t="n">
-        <v>6040</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2006</v>
+        <v>1653</v>
       </c>
       <c r="C5" t="n">
-        <v>6906</v>
+        <v>6335</v>
       </c>
       <c r="D5" t="n">
-        <v>2521</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1101</v>
+        <v>894</v>
       </c>
       <c r="C6" t="n">
-        <v>4991</v>
+        <v>4346</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>495</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>2701</v>
+        <v>2329</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>1169</v>
+        <v>1076</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
         <v>307</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7549</v>
+        <v>6252</v>
       </c>
       <c r="C2" t="n">
-        <v>14784</v>
+        <v>8096</v>
       </c>
       <c r="D2" t="n">
-        <v>23631</v>
+        <v>43369</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3806</v>
+        <v>3062</v>
       </c>
       <c r="C3" t="n">
-        <v>7213</v>
+        <v>10053</v>
       </c>
       <c r="D3" t="n">
-        <v>11860</v>
+        <v>17735</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2924</v>
+        <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>6598</v>
+        <v>8811</v>
       </c>
       <c r="D4" t="n">
-        <v>6610</v>
+        <v>7664</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2170</v>
+        <v>1790</v>
       </c>
       <c r="C5" t="n">
-        <v>6929</v>
+        <v>6807</v>
       </c>
       <c r="D5" t="n">
-        <v>2926</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1328</v>
+        <v>1086</v>
       </c>
       <c r="C6" t="n">
-        <v>5687</v>
+        <v>5146</v>
       </c>
       <c r="D6" t="n">
-        <v>1306</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>662</v>
+        <v>538</v>
       </c>
       <c r="C7" t="n">
-        <v>3642</v>
+        <v>3135</v>
       </c>
       <c r="D7" t="n">
-        <v>702</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="C8" t="n">
-        <v>1757</v>
+        <v>1579</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>713</v>
+        <v>674</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7372</v>
+        <v>6436</v>
       </c>
       <c r="C2" t="n">
-        <v>13252</v>
+        <v>7544</v>
       </c>
       <c r="D2" t="n">
-        <v>25811</v>
+        <v>32227</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4253</v>
+        <v>3446</v>
       </c>
       <c r="C3" t="n">
-        <v>8934</v>
+        <v>8317</v>
       </c>
       <c r="D3" t="n">
-        <v>12438</v>
+        <v>19499</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2771</v>
+        <v>2283</v>
       </c>
       <c r="C4" t="n">
-        <v>6639</v>
+        <v>9128</v>
       </c>
       <c r="D4" t="n">
-        <v>7051</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2185</v>
+        <v>1799</v>
       </c>
       <c r="C5" t="n">
-        <v>6591</v>
+        <v>7369</v>
       </c>
       <c r="D5" t="n">
-        <v>3332</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1488</v>
+        <v>1221</v>
       </c>
       <c r="C6" t="n">
-        <v>6049</v>
+        <v>5675</v>
       </c>
       <c r="D6" t="n">
-        <v>1478</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>808</v>
+        <v>659</v>
       </c>
       <c r="C7" t="n">
-        <v>4402</v>
+        <v>3851</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>357</v>
+        <v>296</v>
       </c>
       <c r="C8" t="n">
-        <v>2404</v>
+        <v>2142</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>1063</v>
+        <v>977</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6956</v>
+        <v>6006</v>
       </c>
       <c r="C2" t="n">
-        <v>9435</v>
+        <v>5371</v>
       </c>
       <c r="D2" t="n">
-        <v>21365</v>
+        <v>26904</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4933</v>
+        <v>4029</v>
       </c>
       <c r="C3" t="n">
-        <v>12738</v>
+        <v>12679</v>
       </c>
       <c r="D3" t="n">
-        <v>13457</v>
+        <v>20355</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2018</v>
+        <v>1662</v>
       </c>
       <c r="C4" t="n">
-        <v>9705</v>
+        <v>11806</v>
       </c>
       <c r="D4" t="n">
-        <v>6870</v>
+        <v>8092</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1374</v>
+        <v>1128</v>
       </c>
       <c r="C5" t="n">
-        <v>5928</v>
+        <v>5561</v>
       </c>
       <c r="D5" t="n">
-        <v>2312</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>746</v>
+        <v>608</v>
       </c>
       <c r="C6" t="n">
-        <v>4313</v>
+        <v>3773</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>2355</v>
+        <v>2099</v>
       </c>
       <c r="D7" t="n">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>1041</v>
+        <v>957</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
         <v>78</v>
@@ -1898,10 +1898,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4264</v>
+        <v>3677</v>
       </c>
       <c r="C2" t="n">
-        <v>4607</v>
+        <v>3465</v>
       </c>
       <c r="D2" t="n">
-        <v>15082</v>
+        <v>18642</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4972</v>
+        <v>4160</v>
       </c>
       <c r="C3" t="n">
-        <v>10348</v>
+        <v>8756</v>
       </c>
       <c r="D3" t="n">
-        <v>13715</v>
+        <v>20053</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2668</v>
+        <v>2188</v>
       </c>
       <c r="C4" t="n">
-        <v>11092</v>
+        <v>12277</v>
       </c>
       <c r="D4" t="n">
-        <v>7741</v>
+        <v>9767</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1525</v>
+        <v>1253</v>
       </c>
       <c r="C5" t="n">
-        <v>7539</v>
+        <v>8110</v>
       </c>
       <c r="D5" t="n">
-        <v>2811</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>868</v>
+        <v>709</v>
       </c>
       <c r="C6" t="n">
-        <v>5048</v>
+        <v>4534</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>305</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>3041</v>
+        <v>2693</v>
       </c>
       <c r="D7" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>1256</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2170,7 +2170,7 @@
         <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3826</v>
+        <v>3590</v>
       </c>
       <c r="C2" t="n">
-        <v>16129</v>
+        <v>6014</v>
       </c>
       <c r="D2" t="n">
-        <v>18797</v>
+        <v>18654</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3948</v>
+        <v>3338</v>
       </c>
       <c r="C3" t="n">
-        <v>6971</v>
+        <v>5701</v>
       </c>
       <c r="D3" t="n">
-        <v>12990</v>
+        <v>18556</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3106</v>
+        <v>2575</v>
       </c>
       <c r="C4" t="n">
-        <v>10518</v>
+        <v>10399</v>
       </c>
       <c r="D4" t="n">
-        <v>8423</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1762</v>
+        <v>1446</v>
       </c>
       <c r="C5" t="n">
-        <v>8951</v>
+        <v>9859</v>
       </c>
       <c r="D5" t="n">
-        <v>3435</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1026</v>
+        <v>840</v>
       </c>
       <c r="C6" t="n">
-        <v>6103</v>
+        <v>5969</v>
       </c>
       <c r="D6" t="n">
-        <v>1146</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>370</v>
       </c>
       <c r="C7" t="n">
-        <v>3846</v>
+        <v>3458</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>1802</v>
       </c>
       <c r="D8" t="n">
         <v>344</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>784</v>
+        <v>722</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2359</v>
+        <v>2191</v>
       </c>
       <c r="C2" t="n">
-        <v>8027</v>
+        <v>2977</v>
       </c>
       <c r="D2" t="n">
-        <v>13266</v>
+        <v>13158</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3789</v>
+        <v>3277</v>
       </c>
       <c r="C3" t="n">
-        <v>9520</v>
+        <v>5652</v>
       </c>
       <c r="D3" t="n">
-        <v>13277</v>
+        <v>18179</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3390</v>
+        <v>2814</v>
       </c>
       <c r="C4" t="n">
-        <v>10354</v>
+        <v>9882</v>
       </c>
       <c r="D4" t="n">
-        <v>8987</v>
+        <v>11895</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1812</v>
+        <v>1486</v>
       </c>
       <c r="C5" t="n">
-        <v>10776</v>
+        <v>11598</v>
       </c>
       <c r="D5" t="n">
-        <v>3528</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>803</v>
+        <v>660</v>
       </c>
       <c r="C6" t="n">
-        <v>6971</v>
+        <v>6732</v>
       </c>
       <c r="D6" t="n">
-        <v>1127</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>3840</v>
+        <v>3440</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>1323</v>
+        <v>1202</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
         <v>95</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2625</v>
+        <v>2254</v>
       </c>
       <c r="C2" t="n">
-        <v>11583</v>
+        <v>3793</v>
       </c>
       <c r="D2" t="n">
-        <v>14941</v>
+        <v>12285</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2783</v>
+        <v>2452</v>
       </c>
       <c r="C3" t="n">
-        <v>7953</v>
+        <v>4049</v>
       </c>
       <c r="D3" t="n">
-        <v>12532</v>
+        <v>16518</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3097</v>
+        <v>2611</v>
       </c>
       <c r="C4" t="n">
-        <v>9869</v>
+        <v>7903</v>
       </c>
       <c r="D4" t="n">
-        <v>9331</v>
+        <v>12438</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2141</v>
+        <v>1766</v>
       </c>
       <c r="C5" t="n">
-        <v>10377</v>
+        <v>10648</v>
       </c>
       <c r="D5" t="n">
-        <v>4154</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1049</v>
+        <v>861</v>
       </c>
       <c r="C6" t="n">
-        <v>8477</v>
+        <v>8655</v>
       </c>
       <c r="D6" t="n">
-        <v>1412</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>5079</v>
+        <v>4731</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2187</v>
+        <v>1970</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>602</v>
+        <v>565</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1840</v>
+        <v>1631</v>
       </c>
       <c r="C2" t="n">
-        <v>6235</v>
+        <v>2701</v>
       </c>
       <c r="D2" t="n">
-        <v>11609</v>
+        <v>9114</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2402</v>
+        <v>2102</v>
       </c>
       <c r="C3" t="n">
-        <v>8532</v>
+        <v>3615</v>
       </c>
       <c r="D3" t="n">
-        <v>12260</v>
+        <v>15171</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>2343</v>
       </c>
       <c r="C4" t="n">
-        <v>9154</v>
+        <v>6523</v>
       </c>
       <c r="D4" t="n">
-        <v>9505</v>
+        <v>12807</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2281</v>
+        <v>1913</v>
       </c>
       <c r="C5" t="n">
-        <v>10393</v>
+        <v>9837</v>
       </c>
       <c r="D5" t="n">
-        <v>4564</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1195</v>
+        <v>980</v>
       </c>
       <c r="C6" t="n">
-        <v>9352</v>
+        <v>9580</v>
       </c>
       <c r="D6" t="n">
-        <v>1647</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="C7" t="n">
-        <v>6074</v>
+        <v>5899</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2816</v>
+        <v>2533</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3095</v>
+        <v>2340</v>
       </c>
       <c r="C2" t="n">
-        <v>13078</v>
+        <v>4277</v>
       </c>
       <c r="D2" t="n">
-        <v>12182</v>
+        <v>10380</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1877</v>
+        <v>1643</v>
       </c>
       <c r="C3" t="n">
-        <v>6959</v>
+        <v>2933</v>
       </c>
       <c r="D3" t="n">
-        <v>11422</v>
+        <v>13545</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2311</v>
+        <v>1968</v>
       </c>
       <c r="C4" t="n">
-        <v>8724</v>
+        <v>5242</v>
       </c>
       <c r="D4" t="n">
-        <v>9586</v>
+        <v>12735</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2227</v>
+        <v>1891</v>
       </c>
       <c r="C5" t="n">
-        <v>9724</v>
+        <v>8391</v>
       </c>
       <c r="D5" t="n">
-        <v>5041</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1418</v>
+        <v>1165</v>
       </c>
       <c r="C6" t="n">
-        <v>9640</v>
+        <v>9596</v>
       </c>
       <c r="D6" t="n">
-        <v>1962</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="C7" t="n">
-        <v>7163</v>
+        <v>7159</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>783</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>3836</v>
+        <v>3645</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1267</v>
+        <v>1171</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6858</v>
+        <v>4811</v>
       </c>
       <c r="C2" t="n">
-        <v>11760</v>
+        <v>11076</v>
       </c>
       <c r="D2" t="n">
-        <v>15667</v>
+        <v>8751</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2310</v>
+        <v>1727</v>
       </c>
       <c r="C2" t="n">
-        <v>7952</v>
+        <v>2568</v>
       </c>
       <c r="D2" t="n">
-        <v>9160</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2579</v>
+        <v>2220</v>
       </c>
       <c r="C3" t="n">
-        <v>9042</v>
+        <v>3574</v>
       </c>
       <c r="D3" t="n">
-        <v>12286</v>
+        <v>14562</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3219</v>
+        <v>2753</v>
       </c>
       <c r="C4" t="n">
-        <v>11885</v>
+        <v>7948</v>
       </c>
       <c r="D4" t="n">
-        <v>9724</v>
+        <v>12818</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1310</v>
+        <v>1076</v>
       </c>
       <c r="C5" t="n">
-        <v>13910</v>
+        <v>13041</v>
       </c>
       <c r="D5" t="n">
-        <v>4561</v>
+        <v>5564</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>416</v>
+        <v>353</v>
       </c>
       <c r="C6" t="n">
-        <v>8531</v>
+        <v>8614</v>
       </c>
       <c r="D6" t="n">
-        <v>1605</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3759</v>
+        <v>3572</v>
       </c>
       <c r="D7" t="n">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1241</v>
+        <v>1147</v>
       </c>
       <c r="D8" t="n">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" t="n">
         <v>35</v>
-      </c>
-      <c r="D13" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7508</v>
+        <v>6224</v>
       </c>
       <c r="C2" t="n">
-        <v>8379</v>
+        <v>5356</v>
       </c>
       <c r="D2" t="n">
-        <v>14481</v>
+        <v>14301</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2913</v>
+        <v>2045</v>
       </c>
       <c r="C3" t="n">
-        <v>5927</v>
+        <v>5582</v>
       </c>
       <c r="D3" t="n">
-        <v>3271</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4750</v>
+        <v>3990</v>
       </c>
       <c r="C2" t="n">
-        <v>10354</v>
+        <v>9581</v>
       </c>
       <c r="D2" t="n">
-        <v>14165</v>
+        <v>19773</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4279</v>
+        <v>3393</v>
       </c>
       <c r="C3" t="n">
-        <v>6308</v>
+        <v>4703</v>
       </c>
       <c r="D3" t="n">
-        <v>4913</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1300</v>
+        <v>922</v>
       </c>
       <c r="C4" t="n">
-        <v>3516</v>
+        <v>3314</v>
       </c>
       <c r="D4" t="n">
-        <v>1840</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5869</v>
+        <v>4938</v>
       </c>
       <c r="C2" t="n">
-        <v>14704</v>
+        <v>10174</v>
       </c>
       <c r="D2" t="n">
-        <v>21482</v>
+        <v>24517</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>3038</v>
       </c>
       <c r="C3" t="n">
-        <v>7347</v>
+        <v>6373</v>
       </c>
       <c r="D3" t="n">
-        <v>6039</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2336</v>
+        <v>1832</v>
       </c>
       <c r="C4" t="n">
-        <v>4997</v>
+        <v>4031</v>
       </c>
       <c r="D4" t="n">
-        <v>2374</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>584</v>
+        <v>431</v>
       </c>
       <c r="C5" t="n">
-        <v>1987</v>
+        <v>1908</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7426</v>
+        <v>5923</v>
       </c>
       <c r="C2" t="n">
-        <v>12643</v>
+        <v>14508</v>
       </c>
       <c r="D2" t="n">
-        <v>23570</v>
+        <v>25460</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3888</v>
+        <v>3214</v>
       </c>
       <c r="C3" t="n">
-        <v>9643</v>
+        <v>7249</v>
       </c>
       <c r="D3" t="n">
-        <v>7961</v>
+        <v>8576</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2586</v>
+        <v>2049</v>
       </c>
       <c r="C4" t="n">
-        <v>6133</v>
+        <v>5206</v>
       </c>
       <c r="D4" t="n">
-        <v>2970</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1183</v>
+        <v>929</v>
       </c>
       <c r="C5" t="n">
-        <v>3477</v>
+        <v>2968</v>
       </c>
       <c r="D5" t="n">
-        <v>1419</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>312</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>1123</v>
+        <v>1098</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7516</v>
+        <v>5941</v>
       </c>
       <c r="C2" t="n">
-        <v>9684</v>
+        <v>9063</v>
       </c>
       <c r="D2" t="n">
-        <v>22213</v>
+        <v>20748</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4059</v>
+        <v>3260</v>
       </c>
       <c r="C3" t="n">
-        <v>9120</v>
+        <v>8924</v>
       </c>
       <c r="D3" t="n">
-        <v>9078</v>
+        <v>9914</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1971</v>
+        <v>1611</v>
       </c>
       <c r="C4" t="n">
-        <v>6536</v>
+        <v>5164</v>
       </c>
       <c r="D4" t="n">
-        <v>3234</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>967</v>
+        <v>770</v>
       </c>
       <c r="C5" t="n">
-        <v>3477</v>
+        <v>2976</v>
       </c>
       <c r="D5" t="n">
-        <v>1331</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>347</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>1523</v>
+        <v>1362</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>32</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5824</v>
+        <v>5073</v>
       </c>
       <c r="C2" t="n">
-        <v>8010</v>
+        <v>11991</v>
       </c>
       <c r="D2" t="n">
-        <v>17978</v>
+        <v>27187</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4761</v>
+        <v>3804</v>
       </c>
       <c r="C3" t="n">
-        <v>8140</v>
+        <v>7750</v>
       </c>
       <c r="D3" t="n">
-        <v>10616</v>
+        <v>11004</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2620</v>
+        <v>2130</v>
       </c>
       <c r="C4" t="n">
-        <v>7913</v>
+        <v>7294</v>
       </c>
       <c r="D4" t="n">
-        <v>4313</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1287</v>
+        <v>1049</v>
       </c>
       <c r="C5" t="n">
-        <v>5137</v>
+        <v>4174</v>
       </c>
       <c r="D5" t="n">
-        <v>1655</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>602</v>
+        <v>484</v>
       </c>
       <c r="C6" t="n">
-        <v>2559</v>
+        <v>2230</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1040</v>
+        <v>959</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5036</v>
+        <v>3715</v>
       </c>
       <c r="C2" t="n">
-        <v>7153</v>
+        <v>15733</v>
       </c>
       <c r="D2" t="n">
-        <v>16162</v>
+        <v>34815</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4380</v>
+        <v>3665</v>
       </c>
       <c r="C3" t="n">
-        <v>7026</v>
+        <v>8667</v>
       </c>
       <c r="D3" t="n">
-        <v>10987</v>
+        <v>12689</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3093</v>
+        <v>2503</v>
       </c>
       <c r="C4" t="n">
-        <v>7870</v>
+        <v>7391</v>
       </c>
       <c r="D4" t="n">
-        <v>5331</v>
+        <v>5493</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1670</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>6419</v>
+        <v>5694</v>
       </c>
       <c r="D5" t="n">
-        <v>2048</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>845</v>
+        <v>691</v>
       </c>
       <c r="C6" t="n">
-        <v>3842</v>
+        <v>3212</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>1798</v>
+        <v>1606</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>675</v>
+        <v>642</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_51_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4724</v>
+        <v>8059</v>
       </c>
       <c r="C2" t="n">
-        <v>12475</v>
+        <v>12866</v>
       </c>
       <c r="D2" t="n">
-        <v>44048</v>
+        <v>25424</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3057</v>
+        <v>4128</v>
       </c>
       <c r="C3" t="n">
-        <v>10538</v>
+        <v>6161</v>
       </c>
       <c r="D3" t="n">
-        <v>15002</v>
+        <v>16278</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2579</v>
+        <v>3020</v>
       </c>
       <c r="C4" t="n">
-        <v>7874</v>
+        <v>6137</v>
       </c>
       <c r="D4" t="n">
-        <v>6569</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>2104</v>
       </c>
       <c r="C5" t="n">
-        <v>6335</v>
+        <v>4514</v>
       </c>
       <c r="D5" t="n">
-        <v>2543</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>894</v>
+        <v>1277</v>
       </c>
       <c r="C6" t="n">
-        <v>4346</v>
+        <v>2647</v>
       </c>
       <c r="D6" t="n">
-        <v>1093</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>648</v>
       </c>
       <c r="C7" t="n">
-        <v>2329</v>
+        <v>1502</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="C8" t="n">
-        <v>1076</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
         <v>427</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>433</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6252</v>
+        <v>9631</v>
       </c>
       <c r="C2" t="n">
-        <v>8096</v>
+        <v>11287</v>
       </c>
       <c r="D2" t="n">
-        <v>43369</v>
+        <v>25820</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3062</v>
+        <v>4718</v>
       </c>
       <c r="C3" t="n">
-        <v>10053</v>
+        <v>8059</v>
       </c>
       <c r="D3" t="n">
-        <v>17735</v>
+        <v>16427</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>2985</v>
       </c>
       <c r="C4" t="n">
-        <v>8811</v>
+        <v>5961</v>
       </c>
       <c r="D4" t="n">
-        <v>7664</v>
+        <v>9348</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1790</v>
+        <v>2215</v>
       </c>
       <c r="C5" t="n">
-        <v>6807</v>
+        <v>5167</v>
       </c>
       <c r="D5" t="n">
-        <v>3021</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1086</v>
+        <v>1501</v>
       </c>
       <c r="C6" t="n">
-        <v>5146</v>
+        <v>3420</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>538</v>
+        <v>819</v>
       </c>
       <c r="C7" t="n">
-        <v>3135</v>
+        <v>2006</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>359</v>
       </c>
       <c r="C8" t="n">
-        <v>1579</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6436</v>
+        <v>12384</v>
       </c>
       <c r="C2" t="n">
-        <v>7544</v>
+        <v>11553</v>
       </c>
       <c r="D2" t="n">
-        <v>32227</v>
+        <v>20859</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3446</v>
+        <v>5383</v>
       </c>
       <c r="C3" t="n">
-        <v>8317</v>
+        <v>8318</v>
       </c>
       <c r="D3" t="n">
-        <v>19499</v>
+        <v>16502</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2283</v>
+        <v>3114</v>
       </c>
       <c r="C4" t="n">
-        <v>9128</v>
+        <v>6686</v>
       </c>
       <c r="D4" t="n">
-        <v>8710</v>
+        <v>9993</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>2245</v>
       </c>
       <c r="C5" t="n">
-        <v>7369</v>
+        <v>5394</v>
       </c>
       <c r="D5" t="n">
-        <v>3553</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1221</v>
+        <v>1631</v>
       </c>
       <c r="C6" t="n">
-        <v>5675</v>
+        <v>4060</v>
       </c>
       <c r="D6" t="n">
-        <v>1474</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>659</v>
+        <v>978</v>
       </c>
       <c r="C7" t="n">
-        <v>3851</v>
+        <v>2573</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="C8" t="n">
-        <v>2142</v>
+        <v>1379</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="C9" t="n">
-        <v>977</v>
+        <v>648</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>420</v>
+        <v>313</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6006</v>
+        <v>11111</v>
       </c>
       <c r="C2" t="n">
-        <v>5371</v>
+        <v>7948</v>
       </c>
       <c r="D2" t="n">
-        <v>26904</v>
+        <v>17479</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4029</v>
+        <v>6047</v>
       </c>
       <c r="C3" t="n">
-        <v>12679</v>
+        <v>12039</v>
       </c>
       <c r="D3" t="n">
-        <v>20355</v>
+        <v>18119</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1662</v>
+        <v>2074</v>
       </c>
       <c r="C4" t="n">
-        <v>11806</v>
+        <v>8836</v>
       </c>
       <c r="D4" t="n">
-        <v>8092</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1128</v>
+        <v>1507</v>
       </c>
       <c r="C5" t="n">
-        <v>5561</v>
+        <v>3978</v>
       </c>
       <c r="D5" t="n">
-        <v>2365</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>608</v>
+        <v>903</v>
       </c>
       <c r="C6" t="n">
-        <v>3773</v>
+        <v>2521</v>
       </c>
       <c r="D6" t="n">
-        <v>745</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>441</v>
       </c>
       <c r="C7" t="n">
-        <v>2099</v>
+        <v>1351</v>
       </c>
       <c r="D7" t="n">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>957</v>
+        <v>635</v>
       </c>
       <c r="D8" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3677</v>
+        <v>6519</v>
       </c>
       <c r="C2" t="n">
-        <v>3465</v>
+        <v>3943</v>
       </c>
       <c r="D2" t="n">
-        <v>18642</v>
+        <v>12030</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4160</v>
+        <v>6955</v>
       </c>
       <c r="C3" t="n">
-        <v>8756</v>
+        <v>9252</v>
       </c>
       <c r="D3" t="n">
-        <v>20053</v>
+        <v>17162</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2188</v>
+        <v>3076</v>
       </c>
       <c r="C4" t="n">
-        <v>12277</v>
+        <v>10467</v>
       </c>
       <c r="D4" t="n">
-        <v>9767</v>
+        <v>10613</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1253</v>
+        <v>1653</v>
       </c>
       <c r="C5" t="n">
-        <v>8110</v>
+        <v>6006</v>
       </c>
       <c r="D5" t="n">
-        <v>2998</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>1064</v>
       </c>
       <c r="C6" t="n">
-        <v>4534</v>
+        <v>3178</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>411</v>
       </c>
       <c r="C7" t="n">
-        <v>2693</v>
+        <v>1765</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>1256</v>
+        <v>852</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3590</v>
+        <v>5968</v>
       </c>
       <c r="C2" t="n">
-        <v>6014</v>
+        <v>5854</v>
       </c>
       <c r="D2" t="n">
-        <v>18654</v>
+        <v>16851</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3338</v>
+        <v>5686</v>
       </c>
       <c r="C3" t="n">
-        <v>5701</v>
+        <v>5960</v>
       </c>
       <c r="D3" t="n">
-        <v>18556</v>
+        <v>15310</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2575</v>
+        <v>4054</v>
       </c>
       <c r="C4" t="n">
-        <v>10399</v>
+        <v>9754</v>
       </c>
       <c r="D4" t="n">
-        <v>11050</v>
+        <v>11359</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1446</v>
+        <v>1988</v>
       </c>
       <c r="C5" t="n">
-        <v>9859</v>
+        <v>7936</v>
       </c>
       <c r="D5" t="n">
-        <v>3881</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>840</v>
+        <v>1203</v>
       </c>
       <c r="C6" t="n">
-        <v>5969</v>
+        <v>4427</v>
       </c>
       <c r="D6" t="n">
-        <v>1167</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>370</v>
+        <v>588</v>
       </c>
       <c r="C7" t="n">
-        <v>3458</v>
+        <v>2359</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>203</v>
       </c>
       <c r="C8" t="n">
-        <v>1802</v>
+        <v>1226</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>722</v>
+        <v>541</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2191</v>
+        <v>3598</v>
       </c>
       <c r="C2" t="n">
-        <v>2977</v>
+        <v>2803</v>
       </c>
       <c r="D2" t="n">
-        <v>13158</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3277</v>
+        <v>5551</v>
       </c>
       <c r="C3" t="n">
-        <v>5652</v>
+        <v>5753</v>
       </c>
       <c r="D3" t="n">
-        <v>18179</v>
+        <v>15127</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2814</v>
+        <v>4469</v>
       </c>
       <c r="C4" t="n">
-        <v>9882</v>
+        <v>9285</v>
       </c>
       <c r="D4" t="n">
-        <v>11895</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1486</v>
+        <v>2084</v>
       </c>
       <c r="C5" t="n">
-        <v>11598</v>
+        <v>9464</v>
       </c>
       <c r="D5" t="n">
-        <v>4000</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>660</v>
+        <v>1021</v>
       </c>
       <c r="C6" t="n">
-        <v>6732</v>
+        <v>5221</v>
       </c>
       <c r="D6" t="n">
-        <v>1146</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>117</v>
+        <v>187</v>
       </c>
       <c r="C7" t="n">
-        <v>3440</v>
+        <v>2389</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1202</v>
+        <v>890</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2254</v>
+        <v>4302</v>
       </c>
       <c r="C2" t="n">
-        <v>3793</v>
+        <v>3371</v>
       </c>
       <c r="D2" t="n">
-        <v>12285</v>
+        <v>12298</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2452</v>
+        <v>4083</v>
       </c>
       <c r="C3" t="n">
-        <v>4049</v>
+        <v>3970</v>
       </c>
       <c r="D3" t="n">
-        <v>16518</v>
+        <v>13797</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>4272</v>
       </c>
       <c r="C4" t="n">
-        <v>7903</v>
+        <v>7464</v>
       </c>
       <c r="D4" t="n">
-        <v>12438</v>
+        <v>12069</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1766</v>
+        <v>2661</v>
       </c>
       <c r="C5" t="n">
-        <v>10648</v>
+        <v>9278</v>
       </c>
       <c r="D5" t="n">
-        <v>4939</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>861</v>
+        <v>1295</v>
       </c>
       <c r="C6" t="n">
-        <v>8655</v>
+        <v>6976</v>
       </c>
       <c r="D6" t="n">
-        <v>1487</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>4731</v>
+        <v>3545</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1970</v>
+        <v>1435</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>565</v>
+        <v>461</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1631</v>
+        <v>3042</v>
       </c>
       <c r="C2" t="n">
-        <v>2701</v>
+        <v>2271</v>
       </c>
       <c r="D2" t="n">
-        <v>9114</v>
+        <v>9137</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2102</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="n">
-        <v>3615</v>
+        <v>3435</v>
       </c>
       <c r="D3" t="n">
-        <v>15171</v>
+        <v>12999</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2343</v>
+        <v>3847</v>
       </c>
       <c r="C4" t="n">
-        <v>6523</v>
+        <v>6148</v>
       </c>
       <c r="D4" t="n">
-        <v>12807</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1913</v>
+        <v>2964</v>
       </c>
       <c r="C5" t="n">
-        <v>9837</v>
+        <v>8725</v>
       </c>
       <c r="D5" t="n">
-        <v>5556</v>
+        <v>6351</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>980</v>
+        <v>1523</v>
       </c>
       <c r="C6" t="n">
-        <v>9580</v>
+        <v>7956</v>
       </c>
       <c r="D6" t="n">
-        <v>1778</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>5899</v>
+        <v>4593</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>2533</v>
+        <v>1898</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>527</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
         <v>35</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2340</v>
+        <v>5132</v>
       </c>
       <c r="C2" t="n">
-        <v>4277</v>
+        <v>7029</v>
       </c>
       <c r="D2" t="n">
-        <v>10380</v>
+        <v>18445</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1643</v>
+        <v>2891</v>
       </c>
       <c r="C3" t="n">
-        <v>2933</v>
+        <v>2660</v>
       </c>
       <c r="D3" t="n">
-        <v>13545</v>
+        <v>11828</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1968</v>
+        <v>3281</v>
       </c>
       <c r="C4" t="n">
-        <v>5242</v>
+        <v>4900</v>
       </c>
       <c r="D4" t="n">
-        <v>12735</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1891</v>
+        <v>2998</v>
       </c>
       <c r="C5" t="n">
-        <v>8391</v>
+        <v>7529</v>
       </c>
       <c r="D5" t="n">
-        <v>6292</v>
+        <v>6921</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1165</v>
+        <v>1848</v>
       </c>
       <c r="C6" t="n">
-        <v>9596</v>
+        <v>8178</v>
       </c>
       <c r="D6" t="n">
-        <v>2190</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>383</v>
+        <v>619</v>
       </c>
       <c r="C7" t="n">
-        <v>7159</v>
+        <v>5810</v>
       </c>
       <c r="D7" t="n">
-        <v>783</v>
+        <v>908</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>3645</v>
+        <v>2840</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1171</v>
+        <v>961</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4811</v>
+        <v>9257</v>
       </c>
       <c r="C2" t="n">
-        <v>11076</v>
+        <v>3454</v>
       </c>
       <c r="D2" t="n">
-        <v>8751</v>
+        <v>8443</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1727</v>
+        <v>3713</v>
       </c>
       <c r="C2" t="n">
-        <v>2568</v>
+        <v>4104</v>
       </c>
       <c r="D2" t="n">
-        <v>7722</v>
+        <v>13723</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2220</v>
+        <v>3963</v>
       </c>
       <c r="C3" t="n">
-        <v>3574</v>
+        <v>3842</v>
       </c>
       <c r="D3" t="n">
-        <v>14562</v>
+        <v>13172</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2753</v>
+        <v>4419</v>
       </c>
       <c r="C4" t="n">
-        <v>7948</v>
+        <v>7391</v>
       </c>
       <c r="D4" t="n">
-        <v>12818</v>
+        <v>12089</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1076</v>
+        <v>1762</v>
       </c>
       <c r="C5" t="n">
-        <v>13041</v>
+        <v>11262</v>
       </c>
       <c r="D5" t="n">
-        <v>5564</v>
+        <v>6292</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>353</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>8614</v>
+        <v>7216</v>
       </c>
       <c r="D6" t="n">
-        <v>1726</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3572</v>
+        <v>2783</v>
       </c>
       <c r="D7" t="n">
-        <v>497</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1147</v>
+        <v>941</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6224</v>
+        <v>8085</v>
       </c>
       <c r="C2" t="n">
-        <v>5356</v>
+        <v>5816</v>
       </c>
       <c r="D2" t="n">
-        <v>14301</v>
+        <v>13577</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2045</v>
+        <v>3930</v>
       </c>
       <c r="C3" t="n">
-        <v>5582</v>
+        <v>1740</v>
       </c>
       <c r="D3" t="n">
-        <v>2109</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3990</v>
+        <v>6240</v>
       </c>
       <c r="C2" t="n">
-        <v>9581</v>
+        <v>8254</v>
       </c>
       <c r="D2" t="n">
-        <v>19773</v>
+        <v>29226</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3393</v>
+        <v>4939</v>
       </c>
       <c r="C3" t="n">
-        <v>4703</v>
+        <v>3489</v>
       </c>
       <c r="D3" t="n">
-        <v>4002</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>922</v>
+        <v>1741</v>
       </c>
       <c r="C4" t="n">
-        <v>3314</v>
+        <v>1062</v>
       </c>
       <c r="D4" t="n">
-        <v>1606</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4938</v>
+        <v>5336</v>
       </c>
       <c r="C2" t="n">
-        <v>10174</v>
+        <v>4199</v>
       </c>
       <c r="D2" t="n">
-        <v>24517</v>
+        <v>29533</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3038</v>
+        <v>4592</v>
       </c>
       <c r="C3" t="n">
-        <v>6373</v>
+        <v>5269</v>
       </c>
       <c r="D3" t="n">
-        <v>6237</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1832</v>
+        <v>2848</v>
       </c>
       <c r="C4" t="n">
-        <v>4031</v>
+        <v>2414</v>
       </c>
       <c r="D4" t="n">
-        <v>2017</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>431</v>
+        <v>759</v>
       </c>
       <c r="C5" t="n">
-        <v>1908</v>
+        <v>676</v>
       </c>
       <c r="D5" t="n">
-        <v>1224</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5923</v>
+        <v>6104</v>
       </c>
       <c r="C2" t="n">
-        <v>14508</v>
+        <v>6362</v>
       </c>
       <c r="D2" t="n">
-        <v>25460</v>
+        <v>35932</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3214</v>
+        <v>4079</v>
       </c>
       <c r="C3" t="n">
-        <v>7249</v>
+        <v>4106</v>
       </c>
       <c r="D3" t="n">
-        <v>8576</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2049</v>
+        <v>3173</v>
       </c>
       <c r="C4" t="n">
-        <v>5206</v>
+        <v>3898</v>
       </c>
       <c r="D4" t="n">
-        <v>2725</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>929</v>
+        <v>1484</v>
       </c>
       <c r="C5" t="n">
-        <v>2968</v>
+        <v>1556</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>387</v>
       </c>
       <c r="C6" t="n">
-        <v>1098</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5941</v>
+        <v>6984</v>
       </c>
       <c r="C2" t="n">
-        <v>9063</v>
+        <v>12300</v>
       </c>
       <c r="D2" t="n">
-        <v>20748</v>
+        <v>32370</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3260</v>
+        <v>3681</v>
       </c>
       <c r="C3" t="n">
-        <v>8924</v>
+        <v>4308</v>
       </c>
       <c r="D3" t="n">
-        <v>9914</v>
+        <v>12759</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1611</v>
+        <v>2239</v>
       </c>
       <c r="C4" t="n">
-        <v>5164</v>
+        <v>3286</v>
       </c>
       <c r="D4" t="n">
-        <v>3237</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>770</v>
+        <v>1225</v>
       </c>
       <c r="C5" t="n">
-        <v>2976</v>
+        <v>2017</v>
       </c>
       <c r="D5" t="n">
-        <v>1218</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>438</v>
       </c>
       <c r="C6" t="n">
-        <v>1362</v>
+        <v>691</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>451</v>
+        <v>268</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>63</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5073</v>
+        <v>5588</v>
       </c>
       <c r="C2" t="n">
-        <v>11991</v>
+        <v>7417</v>
       </c>
       <c r="D2" t="n">
-        <v>27187</v>
+        <v>26231</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3804</v>
+        <v>4435</v>
       </c>
       <c r="C3" t="n">
-        <v>7750</v>
+        <v>7729</v>
       </c>
       <c r="D3" t="n">
-        <v>11004</v>
+        <v>15114</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2130</v>
+        <v>2596</v>
       </c>
       <c r="C4" t="n">
-        <v>7294</v>
+        <v>3835</v>
       </c>
       <c r="D4" t="n">
-        <v>4484</v>
+        <v>5366</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1049</v>
+        <v>1550</v>
       </c>
       <c r="C5" t="n">
-        <v>4174</v>
+        <v>2718</v>
       </c>
       <c r="D5" t="n">
-        <v>1556</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>484</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>2230</v>
+        <v>1426</v>
       </c>
       <c r="D6" t="n">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>959</v>
+        <v>508</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>346</v>
+        <v>246</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3715</v>
+        <v>6109</v>
       </c>
       <c r="C2" t="n">
-        <v>15733</v>
+        <v>7576</v>
       </c>
       <c r="D2" t="n">
-        <v>34815</v>
+        <v>26648</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3665</v>
+        <v>4117</v>
       </c>
       <c r="C3" t="n">
-        <v>8667</v>
+        <v>6542</v>
       </c>
       <c r="D3" t="n">
-        <v>12689</v>
+        <v>15804</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2503</v>
+        <v>3023</v>
       </c>
       <c r="C4" t="n">
-        <v>7391</v>
+        <v>5960</v>
       </c>
       <c r="D4" t="n">
-        <v>5493</v>
+        <v>7074</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>1812</v>
       </c>
       <c r="C5" t="n">
-        <v>5694</v>
+        <v>3272</v>
       </c>
       <c r="D5" t="n">
-        <v>2042</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>691</v>
+        <v>1054</v>
       </c>
       <c r="C6" t="n">
-        <v>3212</v>
+        <v>2091</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>442</v>
       </c>
       <c r="C7" t="n">
-        <v>1606</v>
+        <v>979</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>642</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>227</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_51_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8059</v>
+        <v>849</v>
       </c>
       <c r="C2" t="n">
-        <v>12866</v>
+        <v>2145</v>
       </c>
       <c r="D2" t="n">
-        <v>25424</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4128</v>
+        <v>1444</v>
       </c>
       <c r="C3" t="n">
-        <v>6161</v>
+        <v>5831</v>
       </c>
       <c r="D3" t="n">
-        <v>16278</v>
+        <v>14303</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3020</v>
+        <v>989</v>
       </c>
       <c r="C4" t="n">
-        <v>6137</v>
+        <v>9565</v>
       </c>
       <c r="D4" t="n">
-        <v>8299</v>
+        <v>5459</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2104</v>
+        <v>527</v>
       </c>
       <c r="C5" t="n">
-        <v>4514</v>
+        <v>5469</v>
       </c>
       <c r="D5" t="n">
-        <v>3051</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1277</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>2647</v>
+        <v>1428</v>
       </c>
       <c r="D6" t="n">
-        <v>1178</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>648</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1502</v>
+        <v>499</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>661</v>
+        <v>333</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>53</v>
+      </c>
+      <c r="D17" t="n">
         <v>37</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9631</v>
+        <v>1110</v>
       </c>
       <c r="C2" t="n">
-        <v>11287</v>
+        <v>3277</v>
       </c>
       <c r="D2" t="n">
-        <v>25820</v>
+        <v>16253</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4718</v>
+        <v>978</v>
       </c>
       <c r="C3" t="n">
-        <v>8059</v>
+        <v>3402</v>
       </c>
       <c r="D3" t="n">
-        <v>16427</v>
+        <v>14382</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2985</v>
+        <v>1050</v>
       </c>
       <c r="C4" t="n">
-        <v>5961</v>
+        <v>7322</v>
       </c>
       <c r="D4" t="n">
-        <v>9348</v>
+        <v>6906</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2215</v>
+        <v>662</v>
       </c>
       <c r="C5" t="n">
-        <v>5167</v>
+        <v>7570</v>
       </c>
       <c r="D5" t="n">
-        <v>3735</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1501</v>
+        <v>330</v>
       </c>
       <c r="C6" t="n">
-        <v>3420</v>
+        <v>3443</v>
       </c>
       <c r="D6" t="n">
-        <v>1449</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>819</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2006</v>
+        <v>949</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1008</v>
+        <v>410</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12384</v>
+        <v>578</v>
       </c>
       <c r="C2" t="n">
-        <v>11553</v>
+        <v>1350</v>
       </c>
       <c r="D2" t="n">
-        <v>20859</v>
+        <v>10970</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5383</v>
+        <v>985</v>
       </c>
       <c r="C3" t="n">
-        <v>8318</v>
+        <v>3211</v>
       </c>
       <c r="D3" t="n">
-        <v>16502</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3114</v>
+        <v>1144</v>
       </c>
       <c r="C4" t="n">
-        <v>6686</v>
+        <v>6329</v>
       </c>
       <c r="D4" t="n">
-        <v>9993</v>
+        <v>7888</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2245</v>
+        <v>675</v>
       </c>
       <c r="C5" t="n">
-        <v>5394</v>
+        <v>8433</v>
       </c>
       <c r="D5" t="n">
-        <v>4429</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1631</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>4060</v>
+        <v>4497</v>
       </c>
       <c r="D6" t="n">
-        <v>1723</v>
+        <v>918</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>978</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2573</v>
+        <v>932</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>478</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1379</v>
+        <v>454</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11111</v>
+        <v>636</v>
       </c>
       <c r="C2" t="n">
-        <v>7948</v>
+        <v>4383</v>
       </c>
       <c r="D2" t="n">
-        <v>17479</v>
+        <v>13711</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6047</v>
+        <v>682</v>
       </c>
       <c r="C3" t="n">
-        <v>12039</v>
+        <v>1991</v>
       </c>
       <c r="D3" t="n">
-        <v>18119</v>
+        <v>12869</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2074</v>
+        <v>954</v>
       </c>
       <c r="C4" t="n">
-        <v>8836</v>
+        <v>4611</v>
       </c>
       <c r="D4" t="n">
-        <v>9584</v>
+        <v>8744</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1507</v>
+        <v>789</v>
       </c>
       <c r="C5" t="n">
-        <v>3978</v>
+        <v>7288</v>
       </c>
       <c r="D5" t="n">
-        <v>2879</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>2521</v>
+        <v>6346</v>
       </c>
       <c r="D6" t="n">
-        <v>794</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>441</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>1351</v>
+        <v>2556</v>
       </c>
       <c r="D7" t="n">
-        <v>470</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6519</v>
+        <v>365</v>
       </c>
       <c r="C2" t="n">
-        <v>3943</v>
+        <v>2640</v>
       </c>
       <c r="D2" t="n">
-        <v>12030</v>
+        <v>10463</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6955</v>
+        <v>580</v>
       </c>
       <c r="C3" t="n">
-        <v>9252</v>
+        <v>2763</v>
       </c>
       <c r="D3" t="n">
-        <v>17162</v>
+        <v>12242</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3076</v>
+        <v>794</v>
       </c>
       <c r="C4" t="n">
-        <v>10467</v>
+        <v>3415</v>
       </c>
       <c r="D4" t="n">
-        <v>10613</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>825</v>
       </c>
       <c r="C5" t="n">
-        <v>6006</v>
+        <v>6285</v>
       </c>
       <c r="D5" t="n">
-        <v>3683</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1064</v>
+        <v>487</v>
       </c>
       <c r="C6" t="n">
-        <v>3178</v>
+        <v>7012</v>
       </c>
       <c r="D6" t="n">
-        <v>1007</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>1765</v>
+        <v>3844</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>852</v>
+        <v>1110</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5968</v>
+        <v>1064</v>
       </c>
       <c r="C2" t="n">
-        <v>5854</v>
+        <v>5684</v>
       </c>
       <c r="D2" t="n">
-        <v>16851</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5686</v>
+        <v>414</v>
       </c>
       <c r="C3" t="n">
-        <v>5960</v>
+        <v>2376</v>
       </c>
       <c r="D3" t="n">
-        <v>15310</v>
+        <v>11177</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4054</v>
+        <v>615</v>
       </c>
       <c r="C4" t="n">
-        <v>9754</v>
+        <v>3057</v>
       </c>
       <c r="D4" t="n">
-        <v>11359</v>
+        <v>9412</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1988</v>
+        <v>751</v>
       </c>
       <c r="C5" t="n">
-        <v>7936</v>
+        <v>4831</v>
       </c>
       <c r="D5" t="n">
-        <v>4635</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1203</v>
+        <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>4427</v>
+        <v>6623</v>
       </c>
       <c r="D6" t="n">
-        <v>1379</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>2359</v>
+        <v>5246</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1226</v>
+        <v>2218</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>501</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3598</v>
+        <v>715</v>
       </c>
       <c r="C2" t="n">
-        <v>2803</v>
+        <v>2956</v>
       </c>
       <c r="D2" t="n">
-        <v>11760</v>
+        <v>8410</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5551</v>
+        <v>656</v>
       </c>
       <c r="C3" t="n">
-        <v>5753</v>
+        <v>3484</v>
       </c>
       <c r="D3" t="n">
-        <v>15127</v>
+        <v>12008</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4469</v>
+        <v>994</v>
       </c>
       <c r="C4" t="n">
-        <v>9285</v>
+        <v>4528</v>
       </c>
       <c r="D4" t="n">
-        <v>11944</v>
+        <v>9759</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2084</v>
+        <v>586</v>
       </c>
       <c r="C5" t="n">
-        <v>9464</v>
+        <v>8234</v>
       </c>
       <c r="D5" t="n">
-        <v>4880</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1021</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>5221</v>
+        <v>6828</v>
       </c>
       <c r="D6" t="n">
-        <v>1345</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2389</v>
+        <v>2173</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>890</v>
+        <v>667</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4302</v>
+        <v>370</v>
       </c>
       <c r="C2" t="n">
-        <v>3371</v>
+        <v>1609</v>
       </c>
       <c r="D2" t="n">
-        <v>12298</v>
+        <v>7073</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4083</v>
+        <v>576</v>
       </c>
       <c r="C3" t="n">
-        <v>3970</v>
+        <v>2831</v>
       </c>
       <c r="D3" t="n">
-        <v>13797</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4272</v>
+        <v>694</v>
       </c>
       <c r="C4" t="n">
-        <v>7464</v>
+        <v>3782</v>
       </c>
       <c r="D4" t="n">
-        <v>12069</v>
+        <v>9444</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2661</v>
+        <v>543</v>
       </c>
       <c r="C5" t="n">
-        <v>9278</v>
+        <v>5745</v>
       </c>
       <c r="D5" t="n">
-        <v>5748</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1295</v>
+        <v>215</v>
       </c>
       <c r="C6" t="n">
-        <v>6976</v>
+        <v>6141</v>
       </c>
       <c r="D6" t="n">
-        <v>1802</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
-        <v>3545</v>
+        <v>3032</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1435</v>
+        <v>802</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3042</v>
+        <v>191</v>
       </c>
       <c r="C2" t="n">
-        <v>2271</v>
+        <v>6988</v>
       </c>
       <c r="D2" t="n">
-        <v>9137</v>
+        <v>11261</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3640</v>
+        <v>400</v>
       </c>
       <c r="C3" t="n">
-        <v>3435</v>
+        <v>1886</v>
       </c>
       <c r="D3" t="n">
-        <v>12999</v>
+        <v>9294</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3847</v>
+        <v>554</v>
       </c>
       <c r="C4" t="n">
-        <v>6148</v>
+        <v>3164</v>
       </c>
       <c r="D4" t="n">
-        <v>12033</v>
+        <v>9384</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2964</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>8725</v>
+        <v>4606</v>
       </c>
       <c r="D5" t="n">
-        <v>6351</v>
+        <v>5383</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1523</v>
+        <v>334</v>
       </c>
       <c r="C6" t="n">
-        <v>7956</v>
+        <v>5866</v>
       </c>
       <c r="D6" t="n">
-        <v>2119</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>4593</v>
+        <v>4644</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>1898</v>
+        <v>1880</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5132</v>
+        <v>190</v>
       </c>
       <c r="C2" t="n">
-        <v>7029</v>
+        <v>13437</v>
       </c>
       <c r="D2" t="n">
-        <v>18445</v>
+        <v>12665</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2891</v>
+        <v>256</v>
       </c>
       <c r="C3" t="n">
-        <v>2660</v>
+        <v>3907</v>
       </c>
       <c r="D3" t="n">
-        <v>11828</v>
+        <v>9027</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3281</v>
+        <v>422</v>
       </c>
       <c r="C4" t="n">
-        <v>4900</v>
+        <v>2405</v>
       </c>
       <c r="D4" t="n">
-        <v>11681</v>
+        <v>8993</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2998</v>
+        <v>501</v>
       </c>
       <c r="C5" t="n">
-        <v>7529</v>
+        <v>3776</v>
       </c>
       <c r="D5" t="n">
-        <v>6921</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1848</v>
+        <v>401</v>
       </c>
       <c r="C6" t="n">
-        <v>8178</v>
+        <v>5186</v>
       </c>
       <c r="D6" t="n">
-        <v>2620</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>5810</v>
+        <v>5228</v>
       </c>
       <c r="D7" t="n">
-        <v>908</v>
+        <v>970</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2840</v>
+        <v>3152</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>961</v>
+        <v>1114</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9257</v>
+        <v>2879</v>
       </c>
       <c r="C2" t="n">
-        <v>3454</v>
+        <v>3791</v>
       </c>
       <c r="D2" t="n">
-        <v>8443</v>
+        <v>7581</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3713</v>
+        <v>368</v>
       </c>
       <c r="C2" t="n">
-        <v>4104</v>
+        <v>23989</v>
       </c>
       <c r="D2" t="n">
-        <v>13723</v>
+        <v>11825</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3963</v>
+        <v>191</v>
       </c>
       <c r="C3" t="n">
-        <v>3842</v>
+        <v>7250</v>
       </c>
       <c r="D3" t="n">
-        <v>13172</v>
+        <v>8915</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4419</v>
+        <v>305</v>
       </c>
       <c r="C4" t="n">
-        <v>7391</v>
+        <v>3075</v>
       </c>
       <c r="D4" t="n">
-        <v>12089</v>
+        <v>8725</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1762</v>
+        <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>11262</v>
+        <v>3065</v>
       </c>
       <c r="D5" t="n">
-        <v>6292</v>
+        <v>6147</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>409</v>
       </c>
       <c r="C6" t="n">
-        <v>7216</v>
+        <v>4462</v>
       </c>
       <c r="D6" t="n">
-        <v>2032</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>2783</v>
+        <v>5207</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>941</v>
+        <v>4025</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>1921</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>634</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8085</v>
+        <v>3835</v>
       </c>
       <c r="C2" t="n">
-        <v>5816</v>
+        <v>8162</v>
       </c>
       <c r="D2" t="n">
-        <v>13577</v>
+        <v>12425</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3930</v>
+        <v>953</v>
       </c>
       <c r="C3" t="n">
-        <v>1740</v>
+        <v>1497</v>
       </c>
       <c r="D3" t="n">
-        <v>2057</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6240</v>
+        <v>2151</v>
       </c>
       <c r="C2" t="n">
-        <v>8254</v>
+        <v>9189</v>
       </c>
       <c r="D2" t="n">
-        <v>29226</v>
+        <v>21634</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4939</v>
+        <v>2060</v>
       </c>
       <c r="C3" t="n">
-        <v>3489</v>
+        <v>4747</v>
       </c>
       <c r="D3" t="n">
-        <v>3840</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1741</v>
+        <v>467</v>
       </c>
       <c r="C4" t="n">
-        <v>1062</v>
+        <v>981</v>
       </c>
       <c r="D4" t="n">
-        <v>1595</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5336</v>
+        <v>1277</v>
       </c>
       <c r="C2" t="n">
-        <v>4199</v>
+        <v>10143</v>
       </c>
       <c r="D2" t="n">
-        <v>29533</v>
+        <v>22016</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4592</v>
+        <v>1754</v>
       </c>
       <c r="C3" t="n">
-        <v>5269</v>
+        <v>6317</v>
       </c>
       <c r="D3" t="n">
-        <v>7625</v>
+        <v>6232</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2848</v>
+        <v>1107</v>
       </c>
       <c r="C4" t="n">
-        <v>2414</v>
+        <v>3238</v>
       </c>
       <c r="D4" t="n">
-        <v>1977</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>759</v>
+        <v>249</v>
       </c>
       <c r="C5" t="n">
-        <v>676</v>
+        <v>655</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6104</v>
+        <v>1637</v>
       </c>
       <c r="C2" t="n">
-        <v>6362</v>
+        <v>11281</v>
       </c>
       <c r="D2" t="n">
-        <v>35932</v>
+        <v>22532</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4079</v>
+        <v>1258</v>
       </c>
       <c r="C3" t="n">
-        <v>4106</v>
+        <v>7294</v>
       </c>
       <c r="D3" t="n">
-        <v>10418</v>
+        <v>8308</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3173</v>
+        <v>1228</v>
       </c>
       <c r="C4" t="n">
-        <v>3898</v>
+        <v>4944</v>
       </c>
       <c r="D4" t="n">
-        <v>2947</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1484</v>
+        <v>584</v>
       </c>
       <c r="C5" t="n">
-        <v>1556</v>
+        <v>2079</v>
       </c>
       <c r="D5" t="n">
-        <v>1296</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>289</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6984</v>
+        <v>1551</v>
       </c>
       <c r="C2" t="n">
-        <v>12300</v>
+        <v>7217</v>
       </c>
       <c r="D2" t="n">
-        <v>32370</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3681</v>
+        <v>1185</v>
       </c>
       <c r="C3" t="n">
-        <v>4308</v>
+        <v>8155</v>
       </c>
       <c r="D3" t="n">
-        <v>12759</v>
+        <v>9885</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2239</v>
+        <v>1079</v>
       </c>
       <c r="C4" t="n">
-        <v>3286</v>
+        <v>6127</v>
       </c>
       <c r="D4" t="n">
-        <v>3684</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1225</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>2017</v>
+        <v>3548</v>
       </c>
       <c r="D5" t="n">
-        <v>1238</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>438</v>
+        <v>323</v>
       </c>
       <c r="C6" t="n">
-        <v>691</v>
+        <v>1277</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5588</v>
+        <v>1897</v>
       </c>
       <c r="C2" t="n">
-        <v>7417</v>
+        <v>5434</v>
       </c>
       <c r="D2" t="n">
-        <v>26231</v>
+        <v>36534</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4435</v>
+        <v>1113</v>
       </c>
       <c r="C3" t="n">
-        <v>7729</v>
+        <v>6718</v>
       </c>
       <c r="D3" t="n">
-        <v>15114</v>
+        <v>11035</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2596</v>
+        <v>978</v>
       </c>
       <c r="C4" t="n">
-        <v>3835</v>
+        <v>7050</v>
       </c>
       <c r="D4" t="n">
-        <v>5366</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1550</v>
+        <v>814</v>
       </c>
       <c r="C5" t="n">
-        <v>2718</v>
+        <v>4761</v>
       </c>
       <c r="D5" t="n">
-        <v>1693</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>482</v>
       </c>
       <c r="C6" t="n">
-        <v>1426</v>
+        <v>2353</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>508</v>
+        <v>798</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6109</v>
+        <v>1688</v>
       </c>
       <c r="C2" t="n">
-        <v>7576</v>
+        <v>3347</v>
       </c>
       <c r="D2" t="n">
-        <v>26648</v>
+        <v>28562</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4117</v>
+        <v>1610</v>
       </c>
       <c r="C3" t="n">
-        <v>6542</v>
+        <v>9750</v>
       </c>
       <c r="D3" t="n">
-        <v>15804</v>
+        <v>12503</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3023</v>
+        <v>752</v>
       </c>
       <c r="C4" t="n">
-        <v>5960</v>
+        <v>9037</v>
       </c>
       <c r="D4" t="n">
-        <v>7074</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1812</v>
+        <v>445</v>
       </c>
       <c r="C5" t="n">
-        <v>3272</v>
+        <v>2305</v>
       </c>
       <c r="D5" t="n">
-        <v>2295</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1054</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>2091</v>
+        <v>782</v>
       </c>
       <c r="D6" t="n">
-        <v>988</v>
+        <v>628</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>442</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>979</v>
+        <v>329</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
